--- a/salidas/empresas/MDT.xlsx
+++ b/salidas/empresas/MDT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.59900665283203</v>
+        <v>35.30941009521484</v>
       </c>
       <c r="C2" t="n">
         <v>56.47000122070312</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>34.01037979125977</v>
+        <v>33.73373413085938</v>
       </c>
       <c r="C3" t="n">
         <v>53.95000076293945</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.99308967590332</v>
+        <v>31.73281860351562</v>
       </c>
       <c r="C4" t="n">
         <v>50.75</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.65494918823242</v>
+        <v>31.39744186401367</v>
       </c>
       <c r="C5" t="n">
         <v>50.11999893188477</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.88861846923828</v>
+        <v>31.62921142578125</v>
       </c>
       <c r="C6" t="n">
         <v>50.4900016784668</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>29.63386917114258</v>
+        <v>29.39279937744141</v>
       </c>
       <c r="C7" t="n">
         <v>46.91999816894531</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>31.9826488494873</v>
+        <v>31.72247505187988</v>
       </c>
       <c r="C8" t="n">
         <v>50.52000045776367</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.69092750549316</v>
+        <v>29.44941520690918</v>
       </c>
       <c r="C9" t="n">
         <v>46.90000152587891</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.39972114562988</v>
+        <v>29.16055870056152</v>
       </c>
       <c r="C10" t="n">
         <v>46.43999862670898</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.88971138000488</v>
+        <v>30.63842964172363</v>
       </c>
       <c r="C11" t="n">
         <v>48.68000030517578</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>33.07889556884766</v>
+        <v>32.8098258972168</v>
       </c>
       <c r="C12" t="n">
         <v>52.13000106811523</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>33.95456314086914</v>
+        <v>33.6783561706543</v>
       </c>
       <c r="C13" t="n">
         <v>53.5099983215332</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>33.98637390136719</v>
+        <v>33.70988845825195</v>
       </c>
       <c r="C14" t="n">
         <v>53.45000076293945</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.02155685424805</v>
+        <v>31.76108741760254</v>
       </c>
       <c r="C15" t="n">
         <v>50.36000061035156</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>31.19496154785156</v>
+        <v>30.94118309020996</v>
       </c>
       <c r="C16" t="n">
         <v>49.06000137329102</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>33.73165130615234</v>
+        <v>33.45726013183594</v>
       </c>
       <c r="C17" t="n">
         <v>52.93000030517578</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>33.88459014892578</v>
+        <v>33.60895919799805</v>
       </c>
       <c r="C18" t="n">
         <v>53.16999816894531</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.04976654052734</v>
+        <v>32.78092575073242</v>
       </c>
       <c r="C19" t="n">
         <v>51.86000061035156</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.36717987060547</v>
+        <v>32.10391235351562</v>
       </c>
       <c r="C20" t="n">
         <v>50.66999816894531</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>33.75336456298828</v>
+        <v>33.47877883911133</v>
       </c>
       <c r="C21" t="n">
         <v>52.84000015258789</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>36.03381729125977</v>
+        <v>35.74069595336914</v>
       </c>
       <c r="C22" t="n">
         <v>56.40999984741211</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>30.3701286315918</v>
+        <v>30.12307739257812</v>
       </c>
       <c r="C23" t="n">
         <v>47.43999862670898</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>32.55313491821289</v>
+        <v>32.28832244873047</v>
       </c>
       <c r="C24" t="n">
         <v>50.84999847412109</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>32.18185424804688</v>
+        <v>31.92004013061523</v>
       </c>
       <c r="C25" t="n">
         <v>50.27000045776367</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.84256172180176</v>
+        <v>29.59981727600098</v>
       </c>
       <c r="C26" t="n">
         <v>46.5</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>31.67802810668945</v>
+        <v>31.42035675048828</v>
       </c>
       <c r="C27" t="n">
         <v>49.36000061035156</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.04269027709961</v>
+        <v>30.79016494750977</v>
       </c>
       <c r="C28" t="n">
         <v>48.36999893188477</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.32244491577148</v>
+        <v>31.0676212310791</v>
       </c>
       <c r="C29" t="n">
         <v>48.68000030517578</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.60284423828125</v>
+        <v>32.33766555786133</v>
       </c>
       <c r="C30" t="n">
         <v>50.66999816894531</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>33.29777908325195</v>
+        <v>33.02691650390625</v>
       </c>
       <c r="C31" t="n">
         <v>51.75</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.11663818359375</v>
+        <v>33.83909606933594</v>
       </c>
       <c r="C32" t="n">
         <v>52.83000183105469</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>35.25967025756836</v>
+        <v>34.97282791137695</v>
       </c>
       <c r="C33" t="n">
         <v>54.59999847412109</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>32.35365295410156</v>
+        <v>32.09047317504883</v>
       </c>
       <c r="C34" t="n">
         <v>50.09999847412109</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>26.14246368408203</v>
+        <v>25.92980003356934</v>
       </c>
       <c r="C35" t="n">
         <v>40.33000183105469</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>19.78347969055176</v>
+        <v>19.6225528717041</v>
       </c>
       <c r="C36" t="n">
         <v>30.52000045776367</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.49424171447754</v>
+        <v>20.32753753662109</v>
       </c>
       <c r="C37" t="n">
         <v>31.42000007629395</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>21.84444236755371</v>
+        <v>21.6667423248291</v>
       </c>
       <c r="C38" t="n">
         <v>33.4900016784668</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.30059432983398</v>
+        <v>19.14359092712402</v>
       </c>
       <c r="C39" t="n">
         <v>29.59000015258789</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.22232818603516</v>
+        <v>19.06595993041992</v>
       </c>
       <c r="C40" t="n">
         <v>29.46999931335449</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.00656890869141</v>
+        <v>20.83569145202637</v>
       </c>
       <c r="C41" t="n">
         <v>32</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>22.54924201965332</v>
+        <v>22.36581420898438</v>
       </c>
       <c r="C42" t="n">
         <v>34.34999847412109</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>22.90372467041016</v>
+        <v>22.71740531921387</v>
       </c>
       <c r="C43" t="n">
         <v>34.88999938964844</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>23.39545631408691</v>
+        <v>23.20513725280762</v>
       </c>
       <c r="C44" t="n">
         <v>35.41999816894531</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>25.29773902893066</v>
+        <v>25.09194564819336</v>
       </c>
       <c r="C45" t="n">
         <v>38.29999923706055</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>24.30695533752441</v>
+        <v>24.10923385620117</v>
       </c>
       <c r="C46" t="n">
         <v>36.79999923706055</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>23.71472930908203</v>
+        <v>23.52181816101074</v>
       </c>
       <c r="C47" t="n">
         <v>35.70000076293945</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>28.19196701049805</v>
+        <v>27.96264457702637</v>
       </c>
       <c r="C48" t="n">
         <v>42.43999862670898</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>29.2149658203125</v>
+        <v>28.97730255126953</v>
       </c>
       <c r="C49" t="n">
         <v>43.97999954223633</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.62186622619629</v>
+        <v>28.38904571533203</v>
       </c>
       <c r="C50" t="n">
         <v>42.88999938964844</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>28.96220588684082</v>
+        <v>28.72660064697266</v>
       </c>
       <c r="C51" t="n">
         <v>43.40000152587891</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>30.04994964599609</v>
+        <v>29.80549430847168</v>
       </c>
       <c r="C52" t="n">
         <v>45.02999877929688</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>29.28786468505859</v>
+        <v>29.04960441589355</v>
       </c>
       <c r="C53" t="n">
         <v>43.68999862670898</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>26.26455497741699</v>
+        <v>26.05089569091797</v>
       </c>
       <c r="C54" t="n">
         <v>39.18000030517578</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.31381988525391</v>
+        <v>24.11603927612305</v>
       </c>
       <c r="C55" t="n">
         <v>36.27000045776367</v>
@@ -1572,11 +1584,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>24.93807411193848</v>
+        <v>24.7352123260498</v>
       </c>
       <c r="C56" t="n">
         <v>36.97000122070312</v>
@@ -1601,11 +1613,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>21.21455574035645</v>
+        <v>21.04198455810547</v>
       </c>
       <c r="C57" t="n">
         <v>31.45000076293945</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>22.65134429931641</v>
+        <v>22.46708679199219</v>
       </c>
       <c r="C58" t="n">
         <v>33.58000183105469</v>
@@ -1659,11 +1671,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>23.92322731018066</v>
+        <v>23.72861480712891</v>
       </c>
       <c r="C59" t="n">
         <v>35.22999954223633</v>
@@ -1688,11 +1700,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>22.76882934570312</v>
+        <v>22.58360862731934</v>
       </c>
       <c r="C60" t="n">
         <v>33.52999877929688</v>
@@ -1717,11 +1729,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>25.18628120422363</v>
+        <v>24.98139190673828</v>
       </c>
       <c r="C61" t="n">
         <v>37.09000015258789</v>
@@ -1746,11 +1758,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>26.18029975891113</v>
+        <v>25.96733474731445</v>
       </c>
       <c r="C62" t="n">
         <v>38.31999969482422</v>
@@ -1775,11 +1787,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.27341651916504</v>
+        <v>27.05155754089355</v>
       </c>
       <c r="C63" t="n">
         <v>39.91999816894531</v>
@@ -1804,11 +1816,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>26.88399887084961</v>
+        <v>26.6652889251709</v>
       </c>
       <c r="C64" t="n">
         <v>39.34999847412109</v>
@@ -1833,11 +1845,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>28.68812370300293</v>
+        <v>28.45477104187012</v>
       </c>
       <c r="C65" t="n">
         <v>41.75</v>
@@ -1862,11 +1874,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>27.96663475036621</v>
+        <v>27.7391414642334</v>
       </c>
       <c r="C66" t="n">
         <v>40.70000076293945</v>
@@ -1891,11 +1903,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>26.47554588317871</v>
+        <v>26.26017570495605</v>
       </c>
       <c r="C67" t="n">
         <v>38.52999877929688</v>
@@ -1920,11 +1932,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.9310302734375</v>
+        <v>24.72821998596191</v>
       </c>
       <c r="C68" t="n">
         <v>36.04999923706055</v>
@@ -1949,11 +1961,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>24.25329399108887</v>
+        <v>24.05600166320801</v>
       </c>
       <c r="C69" t="n">
         <v>35.06999969482422</v>
@@ -1978,11 +1990,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.98772048950195</v>
+        <v>22.80072212219238</v>
       </c>
       <c r="C70" t="n">
         <v>33.2400016784668</v>
@@ -2007,11 +2019,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>24.20810317993164</v>
+        <v>24.01117134094238</v>
       </c>
       <c r="C71" t="n">
         <v>34.7400016784668</v>
@@ -2036,11 +2048,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>25.38575744628906</v>
+        <v>25.17925453186035</v>
       </c>
       <c r="C72" t="n">
         <v>36.43000030517578</v>
@@ -2065,11 +2077,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.65400123596191</v>
+        <v>26.43717384338379</v>
       </c>
       <c r="C73" t="n">
         <v>38.25</v>
@@ -2094,11 +2106,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>27.04686737060547</v>
+        <v>26.82684898376465</v>
       </c>
       <c r="C74" t="n">
         <v>38.56999969482422</v>
@@ -2123,11 +2135,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>26.73130226135254</v>
+        <v>26.51384162902832</v>
       </c>
       <c r="C75" t="n">
         <v>38.11999893188477</v>
@@ -2152,11 +2164,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>27.48162841796875</v>
+        <v>27.2580623626709</v>
       </c>
       <c r="C76" t="n">
         <v>39.18999862670898</v>
@@ -2181,11 +2193,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>26.95304870605469</v>
+        <v>26.73378944396973</v>
       </c>
       <c r="C77" t="n">
         <v>38.20000076293945</v>
@@ -2210,11 +2222,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>25.99345588684082</v>
+        <v>25.78200721740723</v>
       </c>
       <c r="C78" t="n">
         <v>36.84000015258789</v>
@@ -2239,11 +2251,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>27.32700347900391</v>
+        <v>27.10470008850098</v>
       </c>
       <c r="C79" t="n">
         <v>38.72999954223633</v>
@@ -2268,11 +2280,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>27.99971199035645</v>
+        <v>27.77192687988281</v>
       </c>
       <c r="C80" t="n">
         <v>39.41999816894531</v>
@@ -2297,11 +2309,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>28.88046455383301</v>
+        <v>28.64552879333496</v>
       </c>
       <c r="C81" t="n">
         <v>40.65999984741211</v>
@@ -2326,11 +2338,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>30.62777328491211</v>
+        <v>30.37862586975098</v>
       </c>
       <c r="C82" t="n">
         <v>43.11999893188477</v>
@@ -2355,11 +2367,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>29.71065330505371</v>
+        <v>29.46897506713867</v>
       </c>
       <c r="C83" t="n">
         <v>41.58000183105469</v>
@@ -2384,11 +2396,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>30.08937454223633</v>
+        <v>29.8446044921875</v>
       </c>
       <c r="C84" t="n">
         <v>42.11000061035156</v>
@@ -2413,11 +2425,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>29.49039077758789</v>
+        <v>29.2504711151123</v>
       </c>
       <c r="C85" t="n">
         <v>41.02000045776367</v>
@@ -2442,11 +2454,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>33.50199127197266</v>
+        <v>33.22946548461914</v>
       </c>
       <c r="C86" t="n">
         <v>46.59999847412109</v>
@@ -2471,11 +2483,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>32.32294082641602</v>
+        <v>32.06000900268555</v>
       </c>
       <c r="C87" t="n">
         <v>44.95999908447266</v>
@@ -2500,11 +2512,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>33.76079559326172</v>
+        <v>33.48617553710938</v>
       </c>
       <c r="C88" t="n">
         <v>46.95999908447266</v>
@@ -2529,11 +2541,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>33.74486541748047</v>
+        <v>33.47037506103516</v>
       </c>
       <c r="C89" t="n">
         <v>46.68000030517578</v>
@@ -2558,11 +2570,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>36.87501907348633</v>
+        <v>36.57506561279297</v>
       </c>
       <c r="C90" t="n">
         <v>51.0099983215332</v>
@@ -2587,11 +2599,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>37.20756530761719</v>
+        <v>36.90489196777344</v>
       </c>
       <c r="C91" t="n">
         <v>51.47000122070312</v>
@@ -2616,11 +2628,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>40.14885711669922</v>
+        <v>39.82225036621094</v>
       </c>
       <c r="C92" t="n">
         <v>55.2400016784668</v>
@@ -2645,11 +2657,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.61230850219727</v>
+        <v>37.30633544921875</v>
       </c>
       <c r="C93" t="n">
         <v>51.75</v>
@@ -2674,11 +2686,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>38.7025146484375</v>
+        <v>38.38767242431641</v>
       </c>
       <c r="C94" t="n">
         <v>53.25</v>
@@ -2703,11 +2715,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>41.93816375732422</v>
+        <v>41.59701156616211</v>
       </c>
       <c r="C95" t="n">
         <v>57.40000152587891</v>
@@ -2732,11 +2744,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>41.87971878051758</v>
+        <v>41.53904342651367</v>
       </c>
       <c r="C96" t="n">
         <v>57.31999969482422</v>
@@ -2761,11 +2773,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>42.13651657104492</v>
+        <v>41.79375839233398</v>
       </c>
       <c r="C97" t="n">
         <v>57.38999938964844</v>
@@ -2790,11 +2802,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>41.52712249755859</v>
+        <v>41.18930053710938</v>
       </c>
       <c r="C98" t="n">
         <v>56.56000137329102</v>
@@ -2819,11 +2831,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>43.50949096679688</v>
+        <v>43.15555191040039</v>
       </c>
       <c r="C99" t="n">
         <v>59.2599983215332</v>
@@ -2848,11 +2860,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>45.18350601196289</v>
+        <v>44.81594848632812</v>
       </c>
       <c r="C100" t="n">
         <v>61.54000091552734</v>
@@ -2877,11 +2889,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>43.38360595703125</v>
+        <v>43.03069305419922</v>
       </c>
       <c r="C101" t="n">
         <v>58.81999969482422</v>
@@ -2906,11 +2918,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>45.01363372802734</v>
+        <v>44.64746856689453</v>
       </c>
       <c r="C102" t="n">
         <v>61.02999877929688</v>
@@ -2935,11 +2947,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>47.02718734741211</v>
+        <v>46.64462661743164</v>
       </c>
       <c r="C103" t="n">
         <v>63.7599983215332</v>
@@ -2964,11 +2976,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>45.75617980957031</v>
+        <v>45.38396453857422</v>
       </c>
       <c r="C104" t="n">
         <v>61.7400016784668</v>
@@ -2993,11 +3005,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>47.31992721557617</v>
+        <v>46.93499755859375</v>
       </c>
       <c r="C105" t="n">
         <v>63.84999847412109</v>
@@ -3022,11 +3034,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.91181564331055</v>
+        <v>45.53833770751953</v>
       </c>
       <c r="C106" t="n">
         <v>61.95000076293945</v>
@@ -3051,11 +3063,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>50.76404190063477</v>
+        <v>50.35107803344727</v>
       </c>
       <c r="C107" t="n">
         <v>68.16000366210938</v>
@@ -3080,11 +3092,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.01670837402344</v>
+        <v>54.56917190551758</v>
       </c>
       <c r="C108" t="n">
         <v>73.87000274658203</v>
@@ -3109,11 +3121,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>53.99642944335938</v>
+        <v>53.55717086791992</v>
       </c>
       <c r="C109" t="n">
         <v>72.19999694824219</v>
@@ -3138,11 +3150,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>53.39815139770508</v>
+        <v>52.96376419067383</v>
       </c>
       <c r="C110" t="n">
         <v>71.40000152587891</v>
@@ -3167,11 +3179,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>58.02746200561523</v>
+        <v>57.55542755126953</v>
       </c>
       <c r="C111" t="n">
         <v>77.58999633789062</v>
@@ -3196,11 +3208,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>58.5567512512207</v>
+        <v>58.0804328918457</v>
       </c>
       <c r="C112" t="n">
         <v>77.98999786376953</v>
@@ -3225,11 +3237,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>55.89884567260742</v>
+        <v>55.44413375854492</v>
       </c>
       <c r="C113" t="n">
         <v>74.44999694824219</v>
@@ -3254,11 +3266,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>57.30288696289062</v>
+        <v>56.83677291870117</v>
       </c>
       <c r="C114" t="n">
         <v>76.31999969482422</v>
@@ -3283,11 +3295,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>55.91838073730469</v>
+        <v>55.46348190307617</v>
       </c>
       <c r="C115" t="n">
         <v>74.09999847412109</v>
@@ -3312,11 +3324,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>59.15574264526367</v>
+        <v>58.67453384399414</v>
       </c>
       <c r="C116" t="n">
         <v>78.38999938964844</v>
@@ -3341,11 +3353,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>54.55246734619141</v>
+        <v>54.10873413085938</v>
       </c>
       <c r="C117" t="n">
         <v>72.29000091552734</v>
@@ -3370,11 +3382,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>50.79035186767578</v>
+        <v>50.37718963623047</v>
       </c>
       <c r="C118" t="n">
         <v>66.94000244140625</v>
@@ -3399,11 +3411,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>56.08638381958008</v>
+        <v>55.63014602661133</v>
       </c>
       <c r="C119" t="n">
         <v>73.91999816894531</v>
@@ -3428,11 +3440,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>57.16382217407227</v>
+        <v>56.69878768920898</v>
       </c>
       <c r="C120" t="n">
         <v>75.33999633789062</v>
@@ -3457,11 +3469,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>58.65328598022461</v>
+        <v>58.17617797851562</v>
       </c>
       <c r="C121" t="n">
         <v>76.91999816894531</v>
@@ -3486,11 +3498,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>57.89076614379883</v>
+        <v>57.41985321044922</v>
       </c>
       <c r="C122" t="n">
         <v>75.91999816894531</v>
@@ -3515,11 +3527,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>59.01167678833008</v>
+        <v>58.53165054321289</v>
       </c>
       <c r="C123" t="n">
         <v>77.38999938964844</v>
@@ -3544,11 +3556,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>57.47967529296875</v>
+        <v>57.01209259033203</v>
       </c>
       <c r="C124" t="n">
         <v>75</v>
@@ -3573,11 +3585,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>60.66020202636719</v>
+        <v>60.166748046875</v>
       </c>
       <c r="C125" t="n">
         <v>79.15000152587891</v>
@@ -3602,11 +3614,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>61.67951202392578</v>
+        <v>61.17777633666992</v>
       </c>
       <c r="C126" t="n">
         <v>80.48000335693359</v>
@@ -3631,11 +3643,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>66.50013732910156</v>
+        <v>65.95917510986328</v>
       </c>
       <c r="C127" t="n">
         <v>86.76999664306641</v>
@@ -3660,11 +3672,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>67.49261474609375</v>
+        <v>66.94361877441406</v>
       </c>
       <c r="C128" t="n">
         <v>87.62999725341797</v>
@@ -3689,11 +3701,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>67.03050231933594</v>
+        <v>66.4852294921875</v>
       </c>
       <c r="C129" t="n">
         <v>87.02999877929688</v>
@@ -3718,11 +3730,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>66.87750244140625</v>
+        <v>66.33351135253906</v>
       </c>
       <c r="C130" t="n">
         <v>86.40000152587891</v>
@@ -3747,11 +3759,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>63.48719787597656</v>
+        <v>62.97074508666992</v>
       </c>
       <c r="C131" t="n">
         <v>82.01999664306641</v>
@@ -3776,11 +3788,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>56.51304244995117</v>
+        <v>56.05332183837891</v>
       </c>
       <c r="C132" t="n">
         <v>73.01000213623047</v>
@@ -3805,11 +3817,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>55.46448516845703</v>
+        <v>55.01330184936523</v>
       </c>
       <c r="C133" t="n">
         <v>71.23000335693359</v>
@@ -3834,11 +3846,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>59.19429779052734</v>
+        <v>58.7127571105957</v>
       </c>
       <c r="C134" t="n">
         <v>76.01999664306641</v>
@@ -3863,11 +3875,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>63.0019645690918</v>
+        <v>62.48948287963867</v>
       </c>
       <c r="C135" t="n">
         <v>80.91000366210938</v>
@@ -3892,11 +3904,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>63.06371688842773</v>
+        <v>62.55071640014648</v>
       </c>
       <c r="C136" t="n">
         <v>80.55999755859375</v>
@@ -3921,11 +3933,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>65.04424285888672</v>
+        <v>64.51512145996094</v>
       </c>
       <c r="C137" t="n">
         <v>83.08999633789062</v>
@@ -3950,11 +3962,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>65.97578430175781</v>
+        <v>65.43912506103516</v>
       </c>
       <c r="C138" t="n">
         <v>84.27999877929688</v>
@@ -3979,11 +3991,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>69.47499084472656</v>
+        <v>68.90982818603516</v>
       </c>
       <c r="C139" t="n">
         <v>88.75</v>
@@ -4008,11 +4020,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>66.07540130615234</v>
+        <v>65.53787994384766</v>
       </c>
       <c r="C140" t="n">
         <v>83.97000122070312</v>
@@ -4037,11 +4049,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>63.43928527832031</v>
+        <v>62.92323684692383</v>
       </c>
       <c r="C141" t="n">
         <v>80.62000274658203</v>
@@ -4066,11 +4078,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>61.56043243408203</v>
+        <v>61.05964660644531</v>
       </c>
       <c r="C142" t="n">
         <v>77.76999664306641</v>
@@ -4095,11 +4107,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>63.73725128173828</v>
+        <v>63.21876907348633</v>
       </c>
       <c r="C143" t="n">
         <v>80.51999664306641</v>
@@ -4124,11 +4136,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>65.01166534423828</v>
+        <v>64.48283386230469</v>
       </c>
       <c r="C144" t="n">
         <v>82.12999725341797</v>
@@ -4153,11 +4165,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>64.28097534179688</v>
+        <v>63.75807952880859</v>
       </c>
       <c r="C145" t="n">
         <v>80.75</v>
@@ -4182,11 +4194,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>68.3726806640625</v>
+        <v>67.81646728515625</v>
       </c>
       <c r="C146" t="n">
         <v>85.88999938964844</v>
@@ -4211,11 +4223,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>63.59637069702148</v>
+        <v>63.07903289794922</v>
       </c>
       <c r="C147" t="n">
         <v>79.88999938964844</v>
@@ -4240,11 +4252,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>64.22820281982422</v>
+        <v>63.70569610595703</v>
       </c>
       <c r="C148" t="n">
         <v>80.22000122070312</v>
@@ -4269,11 +4281,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>64.15615081787109</v>
+        <v>63.63425064086914</v>
       </c>
       <c r="C149" t="n">
         <v>80.12999725341797</v>
@@ -4298,11 +4310,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>69.11215972900391</v>
+        <v>68.54996490478516</v>
       </c>
       <c r="C150" t="n">
         <v>86.31999969482422</v>
@@ -4327,11 +4339,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>68.54368591308594</v>
+        <v>67.98612976074219</v>
       </c>
       <c r="C151" t="n">
         <v>85.61000061035156</v>
@@ -4356,11 +4368,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>72.66529846191406</v>
+        <v>72.07416534423828</v>
       </c>
       <c r="C152" t="n">
         <v>90.23000335693359</v>
@@ -4385,11 +4397,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>77.64223480224609</v>
+        <v>77.01065826416016</v>
       </c>
       <c r="C153" t="n">
         <v>96.41000366210938</v>
@@ -4414,11 +4426,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>79.22071075439453</v>
+        <v>78.57626342773438</v>
       </c>
       <c r="C154" t="n">
         <v>98.37000274658203</v>
@@ -4443,11 +4455,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>72.3350830078125</v>
+        <v>71.74668121337891</v>
       </c>
       <c r="C155" t="n">
         <v>89.81999969482422</v>
@@ -4472,11 +4484,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>78.54421997070312</v>
+        <v>77.90528869628906</v>
       </c>
       <c r="C156" t="n">
         <v>97.52999877929688</v>
@@ -4501,11 +4513,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>73.66862487792969</v>
+        <v>73.06937408447266</v>
       </c>
       <c r="C157" t="n">
         <v>90.95999908447266</v>
@@ -4530,11 +4542,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>71.58718872070312</v>
+        <v>71.00482940673828</v>
       </c>
       <c r="C158" t="n">
         <v>88.38999938964844</v>
@@ -4559,11 +4571,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>73.29608154296875</v>
+        <v>72.69983673095703</v>
       </c>
       <c r="C159" t="n">
         <v>90.5</v>
@@ -4588,11 +4600,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>74.17015075683594</v>
+        <v>73.56681060791016</v>
       </c>
       <c r="C160" t="n">
         <v>91.08000183105469</v>
@@ -4617,11 +4629,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>72.32160949707031</v>
+        <v>71.73330688476562</v>
       </c>
       <c r="C161" t="n">
         <v>88.80999755859375</v>
@@ -4646,11 +4658,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>75.39166259765625</v>
+        <v>74.77837371826172</v>
       </c>
       <c r="C162" t="n">
         <v>92.58000183105469</v>
@@ -4675,11 +4687,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>79.30866241455078</v>
+        <v>78.66347503662109</v>
       </c>
       <c r="C163" t="n">
         <v>97.38999938964844</v>
@@ -4704,11 +4716,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>83.47007751464844</v>
+        <v>82.79105377197266</v>
       </c>
       <c r="C164" t="n">
         <v>101.9400024414062</v>
@@ -4733,11 +4745,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>88.34199523925781</v>
+        <v>87.62338256835938</v>
       </c>
       <c r="C165" t="n">
         <v>107.8899993896484</v>
@@ -4762,11 +4774,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>89.38827514648438</v>
+        <v>88.6611328125</v>
       </c>
       <c r="C166" t="n">
         <v>108.620002746582</v>
@@ -4791,11 +4803,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>89.61869049072266</v>
+        <v>88.88966369628906</v>
       </c>
       <c r="C167" t="n">
         <v>108.9000015258789</v>
@@ -4820,11 +4832,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>91.66780090332031</v>
+        <v>90.92212677001953</v>
       </c>
       <c r="C168" t="n">
         <v>111.3899993896484</v>
@@ -4849,11 +4861,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>93.80832672119141</v>
+        <v>93.04524993896484</v>
       </c>
       <c r="C169" t="n">
         <v>113.4499969482422</v>
@@ -4878,11 +4890,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>95.45381164550781</v>
+        <v>94.67733001708984</v>
       </c>
       <c r="C170" t="n">
         <v>115.4400024414062</v>
@@ -4907,11 +4919,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>83.24095916748047</v>
+        <v>82.56380462646484</v>
       </c>
       <c r="C171" t="n">
         <v>100.6699981689453</v>
@@ -4936,11 +4948,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>75.03378295898438</v>
+        <v>74.42340850830078</v>
       </c>
       <c r="C172" t="n">
         <v>90.18000030517578</v>
@@ -4965,11 +4977,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>81.23250579833984</v>
+        <v>80.57170867919922</v>
       </c>
       <c r="C173" t="n">
         <v>97.62999725341797</v>
@@ -4994,11 +5006,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>82.02296447753906</v>
+        <v>81.35572814941406</v>
       </c>
       <c r="C174" t="n">
         <v>98.58000183105469</v>
@@ -5023,11 +5035,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>76.79937744140625</v>
+        <v>76.17461395263672</v>
       </c>
       <c r="C175" t="n">
         <v>91.69999694824219</v>
@@ -5052,11 +5064,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>80.80266571044922</v>
+        <v>80.14534759521484</v>
       </c>
       <c r="C176" t="n">
         <v>96.48000335693359</v>
@@ -5081,11 +5093,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>90.00685119628906</v>
+        <v>89.27469635009766</v>
       </c>
       <c r="C177" t="n">
         <v>107.4700012207031</v>
@@ -5110,11 +5122,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>87.52667236328125</v>
+        <v>86.81465911865234</v>
       </c>
       <c r="C178" t="n">
         <v>103.9199981689453</v>
@@ -5139,11 +5151,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>84.70514678955078</v>
+        <v>84.01607513427734</v>
       </c>
       <c r="C179" t="n">
         <v>100.5699996948242</v>
@@ -5168,11 +5180,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>95.76388549804688</v>
+        <v>94.98486328125</v>
       </c>
       <c r="C180" t="n">
         <v>113.6999969482422</v>
@@ -5197,11 +5209,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>99.15396118164062</v>
+        <v>98.34739685058594</v>
       </c>
       <c r="C181" t="n">
         <v>117.1399993896484</v>
@@ -5226,11 +5238,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>94.23606109619141</v>
+        <v>93.46949005126953</v>
       </c>
       <c r="C182" t="n">
         <v>111.3300018310547</v>
@@ -5255,11 +5267,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>99.01008605957031</v>
+        <v>98.20465850830078</v>
       </c>
       <c r="C183" t="n">
         <v>116.9700012207031</v>
@@ -5284,11 +5296,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>100.4945983886719</v>
+        <v>99.67710113525391</v>
       </c>
       <c r="C184" t="n">
         <v>118.129997253418</v>
@@ -5313,11 +5325,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>111.3752288818359</v>
+        <v>110.4692230224609</v>
       </c>
       <c r="C185" t="n">
         <v>130.9199981689453</v>
@@ -5342,11 +5354,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>107.6916427612305</v>
+        <v>106.8155975341797</v>
       </c>
       <c r="C186" t="n">
         <v>126.5899963378906</v>
@@ -5371,11 +5383,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>106.1317138671875</v>
+        <v>105.2683486938477</v>
       </c>
       <c r="C187" t="n">
         <v>124.129997253418</v>
@@ -5400,11 +5412,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>112.270622253418</v>
+        <v>111.3573608398438</v>
       </c>
       <c r="C188" t="n">
         <v>131.3099975585938</v>
@@ -5429,11 +5441,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>114.1259689331055</v>
+        <v>113.1976089477539</v>
       </c>
       <c r="C189" t="n">
         <v>133.4799957275391</v>
@@ -5458,11 +5470,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>107.7011566162109</v>
+        <v>106.8250579833984</v>
       </c>
       <c r="C190" t="n">
         <v>125.3499984741211</v>
@@ -5487,11 +5499,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>102.9841461181641</v>
+        <v>102.1463851928711</v>
       </c>
       <c r="C191" t="n">
         <v>119.8600006103516</v>
@@ -5516,11 +5528,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>91.677001953125</v>
+        <v>90.93124389648438</v>
       </c>
       <c r="C192" t="n">
         <v>106.6999969482422</v>
@@ -5545,11 +5557,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>89.45079040527344</v>
+        <v>88.72312927246094</v>
       </c>
       <c r="C193" t="n">
         <v>103.4499969482422</v>
@@ -5574,11 +5586,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>89.48539733886719</v>
+        <v>88.75745391845703</v>
       </c>
       <c r="C194" t="n">
         <v>103.4899978637695</v>
@@ -5603,11 +5615,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>90.78239440917969</v>
+        <v>90.04392242431641</v>
       </c>
       <c r="C195" t="n">
         <v>104.9899978637695</v>
@@ -5632,11 +5644,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>96.50859832763672</v>
+        <v>95.72353363037109</v>
       </c>
       <c r="C196" t="n">
         <v>110.9499969482422</v>
@@ -5661,11 +5673,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>90.77635192871094</v>
+        <v>90.03792572021484</v>
       </c>
       <c r="C197" t="n">
         <v>104.3600006103516</v>
@@ -5690,11 +5702,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>87.11435699462891</v>
+        <v>86.40568542480469</v>
       </c>
       <c r="C198" t="n">
         <v>100.1500015258789</v>
@@ -5719,11 +5731,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>78.66738891601562</v>
+        <v>78.02744293212891</v>
       </c>
       <c r="C199" t="n">
         <v>89.75</v>
@@ -5748,11 +5760,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>81.0953369140625</v>
+        <v>80.43565368652344</v>
       </c>
       <c r="C200" t="n">
         <v>92.51999664306641</v>
@@ -5777,11 +5789,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>77.06334686279297</v>
+        <v>76.43647766113281</v>
       </c>
       <c r="C201" t="n">
         <v>87.91999816894531</v>
@@ -5806,11 +5818,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>71.34465026855469</v>
+        <v>70.76426696777344</v>
       </c>
       <c r="C202" t="n">
         <v>80.75</v>
@@ -5835,11 +5847,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>77.16706085205078</v>
+        <v>76.53933715820312</v>
       </c>
       <c r="C203" t="n">
         <v>87.33999633789062</v>
@@ -5864,11 +5876,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>69.83380889892578</v>
+        <v>69.2657470703125</v>
       </c>
       <c r="C204" t="n">
         <v>79.04000091552734</v>
@@ -5893,11 +5905,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>69.27840423583984</v>
+        <v>68.71485900878906</v>
       </c>
       <c r="C205" t="n">
         <v>77.72000122070312</v>
@@ -5922,11 +5934,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>74.5999755859375</v>
+        <v>73.99313354492188</v>
       </c>
       <c r="C206" t="n">
         <v>83.69000244140625</v>
@@ -5951,11 +5963,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>73.80664825439453</v>
+        <v>73.20624542236328</v>
       </c>
       <c r="C207" t="n">
         <v>82.80000305175781</v>
@@ -5980,11 +5992,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>72.47997283935547</v>
+        <v>71.89037322998047</v>
       </c>
       <c r="C208" t="n">
         <v>80.62000274658203</v>
@@ -6009,11 +6021,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>81.7669677734375</v>
+        <v>81.10182189941406</v>
       </c>
       <c r="C209" t="n">
         <v>90.94999694824219</v>
@@ -6038,11 +6050,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>74.40388488769531</v>
+        <v>73.79864501953125</v>
       </c>
       <c r="C210" t="n">
         <v>82.76000213623047</v>
@@ -6067,11 +6079,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>79.82837677001953</v>
+        <v>79.17900848388672</v>
       </c>
       <c r="C211" t="n">
         <v>88.09999847412109</v>
@@ -6096,11 +6108,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>79.52031707763672</v>
+        <v>78.87344360351562</v>
       </c>
       <c r="C212" t="n">
         <v>87.76000213623047</v>
@@ -6125,11 +6137,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>73.84804534912109</v>
+        <v>73.24732971191406</v>
       </c>
       <c r="C213" t="n">
         <v>81.5</v>
@@ -6154,11 +6166,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>71.60928344726562</v>
+        <v>71.02677154541016</v>
       </c>
       <c r="C214" t="n">
         <v>78.36000061035156</v>
@@ -6183,11 +6195,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>64.48123168945312</v>
+        <v>63.95671081542969</v>
       </c>
       <c r="C215" t="n">
         <v>70.55999755859375</v>
@@ -6212,11 +6224,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>72.44086456298828</v>
+        <v>71.85158538818359</v>
       </c>
       <c r="C216" t="n">
         <v>79.26999664306641</v>
@@ -6241,11 +6253,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>75.91357421875</v>
+        <v>75.29605102539062</v>
       </c>
       <c r="C217" t="n">
         <v>82.37999725341797</v>
@@ -6270,11 +6282,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>80.66854858398438</v>
+        <v>80.01233673095703</v>
       </c>
       <c r="C218" t="n">
         <v>87.54000091552734</v>
@@ -6299,11 +6311,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>76.81666564941406</v>
+        <v>76.19178009033203</v>
       </c>
       <c r="C219" t="n">
         <v>83.36000061035156</v>
@@ -6328,11 +6340,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>80.97397613525391</v>
+        <v>80.31528472900391</v>
       </c>
       <c r="C220" t="n">
         <v>87.15000152587891</v>
@@ -6357,11 +6369,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>74.55368041992188</v>
+        <v>73.94720458984375</v>
       </c>
       <c r="C221" t="n">
         <v>80.23999786376953</v>
@@ -6386,11 +6398,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>75.60359954833984</v>
+        <v>74.98858642578125</v>
       </c>
       <c r="C222" t="n">
         <v>81.37000274658203</v>
@@ -6415,11 +6427,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>73.78315734863281</v>
+        <v>73.18295288085938</v>
       </c>
       <c r="C223" t="n">
         <v>78.70999908447266</v>
@@ -6444,11 +6456,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>75.29237365722656</v>
+        <v>74.67990112304688</v>
       </c>
       <c r="C224" t="n">
         <v>80.31999969482422</v>
@@ -6473,11 +6485,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>83.03533935546875</v>
+        <v>82.35988616943359</v>
       </c>
       <c r="C225" t="n">
         <v>88.58000183105469</v>
@@ -6502,11 +6514,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>85.06022644042969</v>
+        <v>84.36829376220703</v>
       </c>
       <c r="C226" t="n">
         <v>90.02999877929688</v>
@@ -6531,11 +6543,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>84.32328033447266</v>
+        <v>83.63733673095703</v>
       </c>
       <c r="C227" t="n">
         <v>89.25</v>
@@ -6560,11 +6572,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>81.76287078857422</v>
+        <v>81.09775543212891</v>
       </c>
       <c r="C228" t="n">
         <v>86.54000091552734</v>
@@ -6589,11 +6601,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>76.12352752685547</v>
+        <v>75.50430297851562</v>
       </c>
       <c r="C229" t="n">
         <v>79.87999725341797</v>
@@ -6618,11 +6630,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>86.549072265625</v>
+        <v>85.84503173828125</v>
       </c>
       <c r="C230" t="n">
         <v>90.81999969482422</v>
@@ -6647,11 +6659,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>87.69263458251953</v>
+        <v>86.97929382324219</v>
       </c>
       <c r="C231" t="n">
         <v>92.01999664306641</v>
@@ -6676,11 +6688,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>86.31324005126953</v>
+        <v>85.61110687255859</v>
       </c>
       <c r="C232" t="n">
         <v>89.86000061035156</v>
@@ -6705,11 +6717,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>81.41454315185547</v>
+        <v>80.75225830078125</v>
       </c>
       <c r="C233" t="n">
         <v>84.76000213623047</v>
@@ -6734,11 +6746,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>79.70479583740234</v>
+        <v>79.05642700195312</v>
       </c>
       <c r="C234" t="n">
         <v>82.98000335693359</v>
@@ -6763,11 +6775,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>84.42494964599609</v>
+        <v>83.73818206787109</v>
       </c>
       <c r="C235" t="n">
         <v>87.16999816894531</v>
@@ -6792,11 +6804,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>87.39826965332031</v>
+        <v>86.68731689453125</v>
       </c>
       <c r="C236" t="n">
         <v>90.23999786376953</v>
@@ -6821,11 +6833,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>89.88734436035156</v>
+        <v>89.15614318847656</v>
       </c>
       <c r="C237" t="n">
         <v>92.80999755859375</v>
@@ -6850,11 +6862,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>92.94057464599609</v>
+        <v>92.18453216552734</v>
       </c>
       <c r="C238" t="n">
         <v>95.23999786376953</v>
@@ -6879,11 +6891,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>88.51019287109375</v>
+        <v>87.79019165039062</v>
       </c>
       <c r="C239" t="n">
         <v>90.69999694824219</v>
@@ -6908,11 +6920,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>102.786979675293</v>
+        <v>101.9508438110352</v>
       </c>
       <c r="C240" t="n">
         <v>105.3300018310547</v>
@@ -6937,11 +6949,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>94.4300537109375</v>
+        <v>93.66189575195312</v>
       </c>
       <c r="C241" t="n">
         <v>96.05999755859375</v>
@@ -6966,11 +6978,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>101.2129745483398</v>
+        <v>100.3896408081055</v>
       </c>
       <c r="C242" t="n">
         <v>102.9599990844727</v>
@@ -6995,11 +7007,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>96.00290679931641</v>
+        <v>95.22195434570312</v>
       </c>
       <c r="C243" t="n">
         <v>97.66000366210938</v>
@@ -7024,11 +7036,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>85.87518310546875</v>
+        <v>85.17662048339844</v>
       </c>
       <c r="C244" t="n">
         <v>86.65000152587891</v>
@@ -7053,11 +7065,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>80.24597930908203</v>
+        <v>79.59320831298828</v>
       </c>
       <c r="C245" t="n">
         <v>80.97000122070312</v>
@@ -7082,11 +7094,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>73.14999389648438</v>
+        <v>72.55494689941406</v>
       </c>
       <c r="C246" t="n">
         <v>73.80999755859375</v>
@@ -7111,11 +7123,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>78.23000335693359</v>
+        <v>77.5936279296875</v>
       </c>
       <c r="C247" t="n">
         <v>78.23000335693359</v>
@@ -7140,11 +7152,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
-        <v>85.38999938964844</v>
+        <v>84.69538116455078</v>
       </c>
       <c r="C248" t="n">
         <v>85.38999938964844</v>
@@ -7169,11 +7181,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
-        <v>90.65000152587891</v>
+        <v>89.91259765625</v>
       </c>
       <c r="C249" t="n">
         <v>90.65000152587891</v>
@@ -7198,32 +7210,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>89.30000305175781</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="C250" t="n">
-        <v>89.30000305175781</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D250" t="n">
-        <v>156023700</v>
+        <v>166985200</v>
       </c>
       <c r="E250" t="n">
         <v>4.06</v>
       </c>
       <c r="F250" t="n">
-        <v>21.9950746432901</v>
+        <v>21.80049313700258</v>
       </c>
       <c r="G250" t="n">
         <v>1279137890</v>
       </c>
       <c r="H250" t="n">
-        <v>114227017480.619</v>
+        <v>113216497376.4333</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1219756690969415</v>
+        <v>0.1305451126930499</v>
       </c>
     </row>
   </sheetData>
@@ -7255,75 +7267,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39564</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39654</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40065</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7359,13 +7371,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39655</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39745</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40156</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7401,13 +7413,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39746</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39836</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40247</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7443,13 +7455,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39837</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39927</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7476,7 +7488,7 @@
       <c r="I5" t="n">
         <v>1.84</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="K5" t="n">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39928</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40065</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I6" t="n">
         <v>1.6</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="K6" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40156</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I7" t="n">
         <v>1.9</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="K7" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40247</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I8" t="n">
         <v>2.03</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="K8" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40208</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I9" t="n">
         <v>2.79</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="K9" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40445</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I10" t="n">
         <v>3.15</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40445</v>
       </c>
       <c r="K10" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40520</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I11" t="n">
         <v>2.89</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40520</v>
       </c>
       <c r="K11" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40611</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40611</v>
       </c>
       <c r="K12" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40722</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I13" t="n">
         <v>2.86</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40722</v>
       </c>
       <c r="K13" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40793</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I14" t="n">
         <v>2.87</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40793</v>
       </c>
       <c r="K14" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40884</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I15" t="n">
         <v>3.17</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40884</v>
       </c>
       <c r="K15" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40935</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40975</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I16" t="n">
         <v>3.19</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40975</v>
       </c>
       <c r="K16" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40936</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41086</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I17" t="n">
         <v>3.41</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41086</v>
       </c>
       <c r="K17" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41027</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41157</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I18" t="n">
         <v>3.47</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41157</v>
       </c>
       <c r="K18" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41118</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41248</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I19" t="n">
         <v>3.28</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41248</v>
       </c>
       <c r="K19" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41209</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41299</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41339</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I20" t="n">
         <v>3.37</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41339</v>
       </c>
       <c r="K20" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41300</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41449</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I21" t="n">
         <v>3.38</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41449</v>
       </c>
       <c r="K21" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41391</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41481</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41521</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I22" t="n">
         <v>3.48</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41521</v>
       </c>
       <c r="K22" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41482</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41572</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I23" t="n">
         <v>3.74</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="K23" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41573</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41663</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I24" t="n">
         <v>3.52</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="K24" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41664</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41810</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I25" t="n">
         <v>3.01</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41810</v>
       </c>
       <c r="K25" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41755</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41880</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I26" t="n">
         <v>2.95</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41880</v>
       </c>
       <c r="K26" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41846</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41936</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I27" t="n">
         <v>2.89</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="K27" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41937</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42027</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42178</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I28" t="n">
         <v>3.12</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42178</v>
       </c>
       <c r="K28" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42028</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42178</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I29" t="n">
         <v>2.68</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42178</v>
       </c>
       <c r="K29" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42119</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42256</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I30" t="n">
         <v>2.38</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42256</v>
       </c>
       <c r="K30" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I31" t="n">
         <v>1.91</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="K31" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I32" t="n">
         <v>1.7</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="K32" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42399</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42549</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I33" t="n">
         <v>2.48</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42549</v>
       </c>
       <c r="K33" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42620</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I34" t="n">
         <v>2.57</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42620</v>
       </c>
       <c r="K34" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42581</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42671</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42709</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I35" t="n">
         <v>3.01</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42709</v>
       </c>
       <c r="K35" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42672</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42762</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I36" t="n">
         <v>2.83</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="K36" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42763</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42913</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I37" t="n">
         <v>2.89</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42913</v>
       </c>
       <c r="K37" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42854</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42944</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I38" t="n">
         <v>2.97</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="K38" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42945</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43073</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I39" t="n">
         <v>3.65</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43073</v>
       </c>
       <c r="K39" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43036</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43126</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I40" t="n">
         <v>2.029999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="K40" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43127</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I41" t="n">
         <v>2.26</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="K41" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43218</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I42" t="n">
         <v>2.31</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="K42" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43309</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43433</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I43" t="n">
         <v>1.65</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43433</v>
       </c>
       <c r="K43" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43400</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43490</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I44" t="n">
         <v>3.62</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="K44" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43491</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I45" t="n">
         <v>3.42</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="K45" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43582</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I46" t="n">
         <v>3.27</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="K46" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43673</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43802</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I47" t="n">
         <v>3.46</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43802</v>
       </c>
       <c r="K47" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43764</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43854</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I48" t="n">
         <v>3.94</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="K48" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43855</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I49" t="n">
         <v>3.55</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="K49" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43946</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I50" t="n">
         <v>3.27</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="K50" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44168</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I51" t="n">
         <v>2.62</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44168</v>
       </c>
       <c r="K51" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I52" t="n">
         <v>2.14</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="K52" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44226</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I53" t="n">
         <v>2.66</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="K53" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44441</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I54" t="n">
         <v>2.86</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44441</v>
       </c>
       <c r="K54" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I55" t="n">
         <v>3.47</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="K55" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44623</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I56" t="n">
         <v>3.630000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44623</v>
       </c>
       <c r="K56" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44735</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I57" t="n">
         <v>3.73</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44735</v>
       </c>
       <c r="K57" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I58" t="n">
         <v>3.87</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="K58" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I59" t="n">
         <v>3.22</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="K59" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44953</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I60" t="n">
         <v>3.04</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="K60" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I61" t="n">
         <v>2.82</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="K61" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45135</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I62" t="n">
         <v>2.71</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="K62" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45136</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I63" t="n">
         <v>3.07</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="K63" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45227</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45317</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I64" t="n">
         <v>3.14</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="K64" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45318</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I65" t="n">
         <v>2.76</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="K65" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45409</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45531</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I66" t="n">
         <v>2.97</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45531</v>
       </c>
       <c r="K66" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45500</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45622</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I67" t="n">
         <v>3.28</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45622</v>
       </c>
       <c r="K67" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45591</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45681</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I68" t="n">
         <v>3.3</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K68" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45682</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I69" t="n">
         <v>3.61</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="K69" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45773</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I70" t="n">
         <v>3.62</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="K70" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45864</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I71" t="n">
         <v>3.7</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="K71" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45955</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I72" t="n">
         <v>3.58</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K72" t="n">
@@ -10571,13 +10583,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46046</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10604,7 +10616,7 @@
       <c r="I73" t="n">
         <v>3.73</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="K73" t="n">
@@ -10617,13 +10629,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10650,7 +10662,7 @@
       <c r="I74" t="n">
         <v>4.06</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="K74" t="n">
@@ -10687,52 +10699,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40059</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40065</v>
       </c>
       <c r="C2" t="n">
@@ -10761,10 +10773,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40156</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40156</v>
       </c>
       <c r="C3" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40242</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40247</v>
       </c>
       <c r="C4" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40353</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40358</v>
       </c>
       <c r="C5" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40424</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40445</v>
       </c>
       <c r="C6" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40515</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40520</v>
       </c>
       <c r="C7" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40606</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40611</v>
       </c>
       <c r="C8" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40718</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40722</v>
       </c>
       <c r="C9" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40788</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40793</v>
       </c>
       <c r="C10" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40879</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40884</v>
       </c>
       <c r="C11" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40970</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40975</v>
       </c>
       <c r="C12" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41082</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41086</v>
       </c>
       <c r="C13" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41151</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41157</v>
       </c>
       <c r="C14" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41248</v>
       </c>
       <c r="C15" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41339</v>
       </c>
       <c r="C16" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41444</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41449</v>
       </c>
       <c r="C17" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41515</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41521</v>
       </c>
       <c r="C18" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41603</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41611</v>
       </c>
       <c r="C19" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41695</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="C20" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41806</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41810</v>
       </c>
       <c r="C21" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41876</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41880</v>
       </c>
       <c r="C22" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41967</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="C23" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42059</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C24" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42171</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42178</v>
       </c>
       <c r="C25" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42250</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42256</v>
       </c>
       <c r="C26" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42341</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="C27" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42432</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="C28" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42541</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42549</v>
       </c>
       <c r="C29" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42608</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42620</v>
       </c>
       <c r="C30" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42709</v>
       </c>
       <c r="C31" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="C32" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42907</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42913</v>
       </c>
       <c r="C33" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42976</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="C34" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43067</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43073</v>
       </c>
       <c r="C35" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="C36" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43271</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="C37" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43341</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="C38" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43431</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43433</v>
       </c>
       <c r="C39" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43523</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="C40" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43634</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="C41" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43704</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="C42" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43796</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43802</v>
       </c>
       <c r="C43" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43886</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="C44" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43999</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="C45" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44076</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="C46" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44168</v>
       </c>
       <c r="C47" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44258</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="C48" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44370</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="C49" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44441</v>
       </c>
       <c r="C50" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="C51" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44623</v>
       </c>
       <c r="C52" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44732</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44735</v>
       </c>
       <c r="C53" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44802</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="C54" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44893</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="C55" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44984</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="C56" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45093</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="C57" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45163</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="C58" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45254</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="C59" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45343</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="C60" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45460</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="C61" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45526</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45531</v>
       </c>
       <c r="C62" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45616</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45622</v>
       </c>
       <c r="C63" t="n">
@@ -12713,10 +12725,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C64" t="n">
@@ -12745,10 +12757,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45825</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="C65" t="n">
@@ -12777,10 +12789,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45889</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="C66" t="n">
@@ -12809,10 +12821,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45980</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="C67" t="n">
@@ -12841,10 +12853,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46071</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C68" t="n">
@@ -12873,10 +12885,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46185</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="C69" t="n">
@@ -12905,10 +12917,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46268</v>
       </c>
       <c r="C70" t="n">
@@ -12955,12 +12967,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MDT.xlsx
+++ b/salidas/empresas/MDT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.30941009521484</v>
+        <v>35.30941772460938</v>
       </c>
       <c r="C2" t="n">
         <v>56.47000122070312</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>33.73373413085938</v>
+        <v>33.73372650146484</v>
       </c>
       <c r="C3" t="n">
         <v>53.95000076293945</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.73281860351562</v>
+        <v>31.73283386230469</v>
       </c>
       <c r="C4" t="n">
         <v>50.75</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.39744186401367</v>
+        <v>31.3974437713623</v>
       </c>
       <c r="C5" t="n">
         <v>50.11999893188477</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.62921142578125</v>
+        <v>31.62921333312988</v>
       </c>
       <c r="C6" t="n">
         <v>50.4900016784668</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>29.39279937744141</v>
+        <v>29.3928165435791</v>
       </c>
       <c r="C7" t="n">
         <v>46.91999816894531</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>31.72247505187988</v>
+        <v>31.72245788574219</v>
       </c>
       <c r="C8" t="n">
         <v>50.52000045776367</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.16055870056152</v>
+        <v>29.16055679321289</v>
       </c>
       <c r="C10" t="n">
         <v>46.43999862670898</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.63842964172363</v>
+        <v>30.63844108581543</v>
       </c>
       <c r="C11" t="n">
         <v>48.68000030517578</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>32.8098258972168</v>
+        <v>32.809814453125</v>
       </c>
       <c r="C12" t="n">
         <v>52.13000106811523</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>33.6783561706543</v>
+        <v>33.6783447265625</v>
       </c>
       <c r="C13" t="n">
         <v>53.5099983215332</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>33.70988845825195</v>
+        <v>33.70988082885742</v>
       </c>
       <c r="C14" t="n">
         <v>53.45000076293945</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>31.76108741760254</v>
+        <v>31.76109313964844</v>
       </c>
       <c r="C15" t="n">
         <v>50.36000061035156</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>30.94118309020996</v>
+        <v>30.94121551513672</v>
       </c>
       <c r="C16" t="n">
         <v>49.06000137329102</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>33.45726013183594</v>
+        <v>33.4572639465332</v>
       </c>
       <c r="C17" t="n">
         <v>52.93000030517578</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>33.60895919799805</v>
+        <v>33.60896682739258</v>
       </c>
       <c r="C18" t="n">
         <v>53.16999816894531</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>32.78092575073242</v>
+        <v>32.78091049194336</v>
       </c>
       <c r="C19" t="n">
         <v>51.86000061035156</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.10391235351562</v>
+        <v>32.1038932800293</v>
       </c>
       <c r="C20" t="n">
         <v>50.66999816894531</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>33.47877883911133</v>
+        <v>33.47878265380859</v>
       </c>
       <c r="C21" t="n">
         <v>52.84000015258789</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>35.74069595336914</v>
+        <v>35.74069213867188</v>
       </c>
       <c r="C22" t="n">
         <v>56.40999984741211</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>30.12307739257812</v>
+        <v>30.12307167053223</v>
       </c>
       <c r="C23" t="n">
         <v>47.43999862670898</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>32.28832244873047</v>
+        <v>32.28833389282227</v>
       </c>
       <c r="C24" t="n">
         <v>50.84999847412109</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.92004013061523</v>
+        <v>31.9200439453125</v>
       </c>
       <c r="C25" t="n">
         <v>50.27000045776367</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.59981727600098</v>
+        <v>29.59980583190918</v>
       </c>
       <c r="C26" t="n">
         <v>46.5</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.79016494750977</v>
+        <v>30.79016876220703</v>
       </c>
       <c r="C28" t="n">
         <v>48.36999893188477</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.0676212310791</v>
+        <v>31.0676383972168</v>
       </c>
       <c r="C29" t="n">
         <v>48.68000030517578</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.33766555786133</v>
+        <v>32.337646484375</v>
       </c>
       <c r="C30" t="n">
         <v>50.66999816894531</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.83909606933594</v>
+        <v>33.839111328125</v>
       </c>
       <c r="C32" t="n">
         <v>52.83000183105469</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>34.97282791137695</v>
+        <v>34.97283172607422</v>
       </c>
       <c r="C33" t="n">
         <v>54.59999847412109</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>32.09047317504883</v>
+        <v>32.0904655456543</v>
       </c>
       <c r="C34" t="n">
         <v>50.09999847412109</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>25.92980003356934</v>
+        <v>25.92979621887207</v>
       </c>
       <c r="C35" t="n">
         <v>40.33000183105469</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.32753753662109</v>
+        <v>20.32753562927246</v>
       </c>
       <c r="C37" t="n">
         <v>31.42000007629395</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>21.6667423248291</v>
+        <v>21.66674041748047</v>
       </c>
       <c r="C38" t="n">
         <v>33.4900016784668</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.14359092712402</v>
+        <v>19.14359474182129</v>
       </c>
       <c r="C39" t="n">
         <v>29.59000015258789</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.06595993041992</v>
+        <v>19.06595420837402</v>
       </c>
       <c r="C40" t="n">
         <v>29.46999931335449</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.83569145202637</v>
+        <v>20.83568954467773</v>
       </c>
       <c r="C41" t="n">
         <v>32</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>22.36581420898438</v>
+        <v>22.36580467224121</v>
       </c>
       <c r="C42" t="n">
         <v>34.34999847412109</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>22.71740531921387</v>
+        <v>22.71740913391113</v>
       </c>
       <c r="C43" t="n">
         <v>34.88999938964844</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>23.20513725280762</v>
+        <v>23.20514106750488</v>
       </c>
       <c r="C44" t="n">
         <v>35.41999816894531</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>24.10923385620117</v>
+        <v>24.1092414855957</v>
       </c>
       <c r="C46" t="n">
         <v>36.79999923706055</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>23.52181816101074</v>
+        <v>23.52182197570801</v>
       </c>
       <c r="C47" t="n">
         <v>35.70000076293945</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>27.96264457702637</v>
+        <v>27.9626350402832</v>
       </c>
       <c r="C48" t="n">
         <v>42.43999862670898</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>28.97730255126953</v>
+        <v>28.97731590270996</v>
       </c>
       <c r="C49" t="n">
         <v>43.97999954223633</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.38904571533203</v>
+        <v>28.3890380859375</v>
       </c>
       <c r="C50" t="n">
         <v>42.88999938964844</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>28.72660064697266</v>
+        <v>28.72659492492676</v>
       </c>
       <c r="C51" t="n">
         <v>43.40000152587891</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.80549430847168</v>
+        <v>29.80550575256348</v>
       </c>
       <c r="C52" t="n">
         <v>45.02999877929688</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>29.04960441589355</v>
+        <v>29.04961395263672</v>
       </c>
       <c r="C53" t="n">
         <v>43.68999862670898</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>26.05089569091797</v>
+        <v>26.05089950561523</v>
       </c>
       <c r="C54" t="n">
         <v>39.18000030517578</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.11603927612305</v>
+        <v>24.11603164672852</v>
       </c>
       <c r="C55" t="n">
         <v>36.27000045776367</v>
@@ -1588,7 +1588,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>24.7352123260498</v>
+        <v>24.73520469665527</v>
       </c>
       <c r="C56" t="n">
         <v>36.97000122070312</v>
@@ -1617,7 +1617,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>21.04198455810547</v>
+        <v>21.04198837280273</v>
       </c>
       <c r="C57" t="n">
         <v>31.45000076293945</v>
@@ -1675,7 +1675,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>23.72861480712891</v>
+        <v>23.72861862182617</v>
       </c>
       <c r="C59" t="n">
         <v>35.22999954223633</v>
@@ -1704,7 +1704,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>22.58360862731934</v>
+        <v>22.5836124420166</v>
       </c>
       <c r="C60" t="n">
         <v>33.52999877929688</v>
@@ -1733,7 +1733,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>24.98139190673828</v>
+        <v>24.98139953613281</v>
       </c>
       <c r="C61" t="n">
         <v>37.09000015258789</v>
@@ -1762,7 +1762,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.96733474731445</v>
+        <v>25.96733665466309</v>
       </c>
       <c r="C62" t="n">
         <v>38.31999969482422</v>
@@ -1791,7 +1791,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.05155754089355</v>
+        <v>27.05156135559082</v>
       </c>
       <c r="C63" t="n">
         <v>39.91999816894531</v>
@@ -1820,7 +1820,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>26.6652889251709</v>
+        <v>26.66530418395996</v>
       </c>
       <c r="C64" t="n">
         <v>39.34999847412109</v>
@@ -1849,7 +1849,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>28.45477104187012</v>
+        <v>28.45477294921875</v>
       </c>
       <c r="C65" t="n">
         <v>41.75</v>
@@ -1878,7 +1878,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>27.7391414642334</v>
+        <v>27.7391300201416</v>
       </c>
       <c r="C66" t="n">
         <v>40.70000076293945</v>
@@ -1907,7 +1907,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>26.26017570495605</v>
+        <v>26.26016998291016</v>
       </c>
       <c r="C67" t="n">
         <v>38.52999877929688</v>
@@ -1936,7 +1936,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.72821998596191</v>
+        <v>24.72821617126465</v>
       </c>
       <c r="C68" t="n">
         <v>36.04999923706055</v>
@@ -1965,7 +1965,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>24.05600166320801</v>
+        <v>24.05599403381348</v>
       </c>
       <c r="C69" t="n">
         <v>35.06999969482422</v>
@@ -1994,7 +1994,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.80072212219238</v>
+        <v>22.80072402954102</v>
       </c>
       <c r="C70" t="n">
         <v>33.2400016784668</v>
@@ -2023,7 +2023,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>24.01117134094238</v>
+        <v>24.01116943359375</v>
       </c>
       <c r="C71" t="n">
         <v>34.7400016784668</v>
@@ -2052,7 +2052,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>25.17925453186035</v>
+        <v>25.17924880981445</v>
       </c>
       <c r="C72" t="n">
         <v>36.43000030517578</v>
@@ -2110,7 +2110,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>26.82684898376465</v>
+        <v>26.82683944702148</v>
       </c>
       <c r="C74" t="n">
         <v>38.56999969482422</v>
@@ -2139,7 +2139,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>26.51384162902832</v>
+        <v>26.51384353637695</v>
       </c>
       <c r="C75" t="n">
         <v>38.11999893188477</v>
@@ -2168,7 +2168,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>27.2580623626709</v>
+        <v>27.25806999206543</v>
       </c>
       <c r="C76" t="n">
         <v>39.18999862670898</v>
@@ -2197,7 +2197,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>26.73378944396973</v>
+        <v>26.73377799987793</v>
       </c>
       <c r="C77" t="n">
         <v>38.20000076293945</v>
@@ -2226,7 +2226,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>25.78200721740723</v>
+        <v>25.78201866149902</v>
       </c>
       <c r="C78" t="n">
         <v>36.84000015258789</v>
@@ -2255,7 +2255,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>27.10470008850098</v>
+        <v>27.10469055175781</v>
       </c>
       <c r="C79" t="n">
         <v>38.72999954223633</v>
@@ -2284,7 +2284,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>27.77192687988281</v>
+        <v>27.77193450927734</v>
       </c>
       <c r="C80" t="n">
         <v>39.41999816894531</v>
@@ -2313,7 +2313,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>28.64552879333496</v>
+        <v>28.64552307128906</v>
       </c>
       <c r="C81" t="n">
         <v>40.65999984741211</v>
@@ -2342,7 +2342,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>30.37862586975098</v>
+        <v>30.37863159179688</v>
       </c>
       <c r="C82" t="n">
         <v>43.11999893188477</v>
@@ -2371,7 +2371,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>29.46897506713867</v>
+        <v>29.46896934509277</v>
       </c>
       <c r="C83" t="n">
         <v>41.58000183105469</v>
@@ -2400,7 +2400,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>29.8446044921875</v>
+        <v>29.84460258483887</v>
       </c>
       <c r="C84" t="n">
         <v>42.11000061035156</v>
@@ -2429,7 +2429,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>29.2504711151123</v>
+        <v>29.25049018859863</v>
       </c>
       <c r="C85" t="n">
         <v>41.02000045776367</v>
@@ -2458,7 +2458,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>33.22946548461914</v>
+        <v>33.22947692871094</v>
       </c>
       <c r="C86" t="n">
         <v>46.59999847412109</v>
@@ -2487,7 +2487,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>32.06000900268555</v>
+        <v>32.06001663208008</v>
       </c>
       <c r="C87" t="n">
         <v>44.95999908447266</v>
@@ -2545,7 +2545,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>33.47037506103516</v>
+        <v>33.47037124633789</v>
       </c>
       <c r="C89" t="n">
         <v>46.68000030517578</v>
@@ -2574,7 +2574,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>36.57506561279297</v>
+        <v>36.57505416870117</v>
       </c>
       <c r="C90" t="n">
         <v>51.0099983215332</v>
@@ -2603,7 +2603,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>36.90489196777344</v>
+        <v>36.90488433837891</v>
       </c>
       <c r="C91" t="n">
         <v>51.47000122070312</v>
@@ -2632,7 +2632,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>39.82225036621094</v>
+        <v>39.8222541809082</v>
       </c>
       <c r="C92" t="n">
         <v>55.2400016784668</v>
@@ -2690,7 +2690,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>38.38767242431641</v>
+        <v>38.38768768310547</v>
       </c>
       <c r="C94" t="n">
         <v>53.25</v>
@@ -2719,7 +2719,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>41.59701156616211</v>
+        <v>41.59700775146484</v>
       </c>
       <c r="C95" t="n">
         <v>57.40000152587891</v>
@@ -2748,7 +2748,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>41.53904342651367</v>
+        <v>41.5390510559082</v>
       </c>
       <c r="C96" t="n">
         <v>57.31999969482422</v>
@@ -2777,7 +2777,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>41.79375839233398</v>
+        <v>41.79373550415039</v>
       </c>
       <c r="C97" t="n">
         <v>57.38999938964844</v>
@@ -2806,7 +2806,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>41.18930053710938</v>
+        <v>41.18931579589844</v>
       </c>
       <c r="C98" t="n">
         <v>56.56000137329102</v>
@@ -2835,7 +2835,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>43.15555191040039</v>
+        <v>43.15555572509766</v>
       </c>
       <c r="C99" t="n">
         <v>59.2599983215332</v>
@@ -2864,7 +2864,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>44.81594848632812</v>
+        <v>44.81594467163086</v>
       </c>
       <c r="C100" t="n">
         <v>61.54000091552734</v>
@@ -2893,7 +2893,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>43.03069305419922</v>
+        <v>43.03069686889648</v>
       </c>
       <c r="C101" t="n">
         <v>58.81999969482422</v>
@@ -2922,7 +2922,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>44.64746856689453</v>
+        <v>44.6474494934082</v>
       </c>
       <c r="C102" t="n">
         <v>61.02999877929688</v>
@@ -2951,7 +2951,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>46.64462661743164</v>
+        <v>46.64464569091797</v>
       </c>
       <c r="C103" t="n">
         <v>63.7599983215332</v>
@@ -2980,7 +2980,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>45.38396453857422</v>
+        <v>45.38398361206055</v>
       </c>
       <c r="C104" t="n">
         <v>61.7400016784668</v>
@@ -3009,7 +3009,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>46.93499755859375</v>
+        <v>46.93499374389648</v>
       </c>
       <c r="C105" t="n">
         <v>63.84999847412109</v>
@@ -3067,7 +3067,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>50.35107803344727</v>
+        <v>50.35110092163086</v>
       </c>
       <c r="C107" t="n">
         <v>68.16000366210938</v>
@@ -3096,7 +3096,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>54.56917190551758</v>
+        <v>54.56916046142578</v>
       </c>
       <c r="C108" t="n">
         <v>73.87000274658203</v>
@@ -3125,7 +3125,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>53.55717086791992</v>
+        <v>53.55717849731445</v>
       </c>
       <c r="C109" t="n">
         <v>72.19999694824219</v>
@@ -3154,7 +3154,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>52.96376419067383</v>
+        <v>52.9637451171875</v>
       </c>
       <c r="C110" t="n">
         <v>71.40000152587891</v>
@@ -3183,7 +3183,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>57.55542755126953</v>
+        <v>57.5554084777832</v>
       </c>
       <c r="C111" t="n">
         <v>77.58999633789062</v>
@@ -3212,7 +3212,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>58.0804328918457</v>
+        <v>58.08043670654297</v>
       </c>
       <c r="C112" t="n">
         <v>77.98999786376953</v>
@@ -3241,7 +3241,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>55.44413375854492</v>
+        <v>55.44411849975586</v>
       </c>
       <c r="C113" t="n">
         <v>74.44999694824219</v>
@@ -3270,7 +3270,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.83677291870117</v>
+        <v>56.83676147460938</v>
       </c>
       <c r="C114" t="n">
         <v>76.31999969482422</v>
@@ -3299,7 +3299,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>55.46348190307617</v>
+        <v>55.46347808837891</v>
       </c>
       <c r="C115" t="n">
         <v>74.09999847412109</v>
@@ -3328,7 +3328,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>58.67453384399414</v>
+        <v>58.67454528808594</v>
       </c>
       <c r="C116" t="n">
         <v>78.38999938964844</v>
@@ -3357,7 +3357,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>54.10873413085938</v>
+        <v>54.10873031616211</v>
       </c>
       <c r="C117" t="n">
         <v>72.29000091552734</v>
@@ -3444,7 +3444,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>56.69878768920898</v>
+        <v>56.69879913330078</v>
       </c>
       <c r="C120" t="n">
         <v>75.33999633789062</v>
@@ -3473,7 +3473,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>58.17617797851562</v>
+        <v>58.17615509033203</v>
       </c>
       <c r="C121" t="n">
         <v>76.91999816894531</v>
@@ -3502,7 +3502,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>57.41985321044922</v>
+        <v>57.41984558105469</v>
       </c>
       <c r="C122" t="n">
         <v>75.91999816894531</v>
@@ -3560,7 +3560,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>57.01209259033203</v>
+        <v>57.0120849609375</v>
       </c>
       <c r="C124" t="n">
         <v>75</v>
@@ -3589,7 +3589,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>60.166748046875</v>
+        <v>60.1667594909668</v>
       </c>
       <c r="C125" t="n">
         <v>79.15000152587891</v>
@@ -3618,7 +3618,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>61.17777633666992</v>
+        <v>61.17776107788086</v>
       </c>
       <c r="C126" t="n">
         <v>80.48000335693359</v>
@@ -3647,7 +3647,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.95917510986328</v>
+        <v>65.95918273925781</v>
       </c>
       <c r="C127" t="n">
         <v>86.76999664306641</v>
@@ -3676,7 +3676,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>66.94361877441406</v>
+        <v>66.943603515625</v>
       </c>
       <c r="C128" t="n">
         <v>87.62999725341797</v>
@@ -3705,7 +3705,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>66.4852294921875</v>
+        <v>66.48526000976562</v>
       </c>
       <c r="C129" t="n">
         <v>87.02999877929688</v>
@@ -3734,7 +3734,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>66.33351135253906</v>
+        <v>66.33347320556641</v>
       </c>
       <c r="C130" t="n">
         <v>86.40000152587891</v>
@@ -3763,7 +3763,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>62.97074508666992</v>
+        <v>62.97072601318359</v>
       </c>
       <c r="C131" t="n">
         <v>82.01999664306641</v>
@@ -3792,7 +3792,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>56.05332183837891</v>
+        <v>56.05332565307617</v>
       </c>
       <c r="C132" t="n">
         <v>73.01000213623047</v>
@@ -3821,7 +3821,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>55.01330184936523</v>
+        <v>55.0132942199707</v>
       </c>
       <c r="C133" t="n">
         <v>71.23000335693359</v>
@@ -3850,7 +3850,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>58.7127571105957</v>
+        <v>58.71276092529297</v>
       </c>
       <c r="C134" t="n">
         <v>76.01999664306641</v>
@@ -3879,7 +3879,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>62.48948287963867</v>
+        <v>62.48946762084961</v>
       </c>
       <c r="C135" t="n">
         <v>80.91000366210938</v>
@@ -3908,7 +3908,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>62.55071640014648</v>
+        <v>62.55075073242188</v>
       </c>
       <c r="C136" t="n">
         <v>80.55999755859375</v>
@@ -3937,7 +3937,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>64.51512145996094</v>
+        <v>64.51512908935547</v>
       </c>
       <c r="C137" t="n">
         <v>83.08999633789062</v>
@@ -3966,7 +3966,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>65.43912506103516</v>
+        <v>65.43910217285156</v>
       </c>
       <c r="C138" t="n">
         <v>84.27999877929688</v>
@@ -3995,7 +3995,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>68.90982818603516</v>
+        <v>68.90984344482422</v>
       </c>
       <c r="C139" t="n">
         <v>88.75</v>
@@ -4024,7 +4024,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.53787994384766</v>
+        <v>65.53785705566406</v>
       </c>
       <c r="C140" t="n">
         <v>83.97000122070312</v>
@@ -4053,7 +4053,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>62.92323684692383</v>
+        <v>62.92324066162109</v>
       </c>
       <c r="C141" t="n">
         <v>80.62000274658203</v>
@@ -4082,7 +4082,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>61.05964660644531</v>
+        <v>61.05966186523438</v>
       </c>
       <c r="C142" t="n">
         <v>77.76999664306641</v>
@@ -4111,7 +4111,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>63.21876907348633</v>
+        <v>63.21877288818359</v>
       </c>
       <c r="C143" t="n">
         <v>80.51999664306641</v>
@@ -4140,7 +4140,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>64.48283386230469</v>
+        <v>64.48282623291016</v>
       </c>
       <c r="C144" t="n">
         <v>82.12999725341797</v>
@@ -4169,7 +4169,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>63.75807952880859</v>
+        <v>63.758056640625</v>
       </c>
       <c r="C145" t="n">
         <v>80.75</v>
@@ -4198,7 +4198,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>67.81646728515625</v>
+        <v>67.81648254394531</v>
       </c>
       <c r="C146" t="n">
         <v>85.88999938964844</v>
@@ -4227,7 +4227,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>63.07903289794922</v>
+        <v>63.07904052734375</v>
       </c>
       <c r="C147" t="n">
         <v>79.88999938964844</v>
@@ -4256,7 +4256,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>63.70569610595703</v>
+        <v>63.70574188232422</v>
       </c>
       <c r="C148" t="n">
         <v>80.22000122070312</v>
@@ -4314,7 +4314,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>68.54996490478516</v>
+        <v>68.54995727539062</v>
       </c>
       <c r="C150" t="n">
         <v>86.31999969482422</v>
@@ -4372,7 +4372,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>72.07416534423828</v>
+        <v>72.07417297363281</v>
       </c>
       <c r="C152" t="n">
         <v>90.23000335693359</v>
@@ -4401,7 +4401,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>77.01065826416016</v>
+        <v>77.01064300537109</v>
       </c>
       <c r="C153" t="n">
         <v>96.41000366210938</v>
@@ -4488,7 +4488,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>77.90528869628906</v>
+        <v>77.90529632568359</v>
       </c>
       <c r="C156" t="n">
         <v>97.52999877929688</v>
@@ -4517,7 +4517,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>73.06937408447266</v>
+        <v>73.06935119628906</v>
       </c>
       <c r="C157" t="n">
         <v>90.95999908447266</v>
@@ -4546,7 +4546,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>71.00482940673828</v>
+        <v>71.00482177734375</v>
       </c>
       <c r="C158" t="n">
         <v>88.38999938964844</v>
@@ -4575,7 +4575,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>72.69983673095703</v>
+        <v>72.69985961914062</v>
       </c>
       <c r="C159" t="n">
         <v>90.5</v>
@@ -4633,7 +4633,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>71.73330688476562</v>
+        <v>71.7332763671875</v>
       </c>
       <c r="C161" t="n">
         <v>88.80999755859375</v>
@@ -4662,7 +4662,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>74.77837371826172</v>
+        <v>74.77838134765625</v>
       </c>
       <c r="C162" t="n">
         <v>92.58000183105469</v>
@@ -4691,7 +4691,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>78.66347503662109</v>
+        <v>78.66349029541016</v>
       </c>
       <c r="C163" t="n">
         <v>97.38999938964844</v>
@@ -4720,7 +4720,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>82.79105377197266</v>
+        <v>82.79106140136719</v>
       </c>
       <c r="C164" t="n">
         <v>101.9400024414062</v>
@@ -4749,7 +4749,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>87.62338256835938</v>
+        <v>87.62335968017578</v>
       </c>
       <c r="C165" t="n">
         <v>107.8899993896484</v>
@@ -4836,7 +4836,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>90.92212677001953</v>
+        <v>90.92213439941406</v>
       </c>
       <c r="C168" t="n">
         <v>111.3899993896484</v>
@@ -4865,7 +4865,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>93.04524993896484</v>
+        <v>93.04524230957031</v>
       </c>
       <c r="C169" t="n">
         <v>113.4499969482422</v>
@@ -4894,7 +4894,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>94.67733001708984</v>
+        <v>94.67731475830078</v>
       </c>
       <c r="C170" t="n">
         <v>115.4400024414062</v>
@@ -4952,7 +4952,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>74.42340850830078</v>
+        <v>74.42340087890625</v>
       </c>
       <c r="C172" t="n">
         <v>90.18000030517578</v>
@@ -4981,7 +4981,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>80.57170867919922</v>
+        <v>80.57172393798828</v>
       </c>
       <c r="C173" t="n">
         <v>97.62999725341797</v>
@@ -5097,7 +5097,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>89.27469635009766</v>
+        <v>89.27467346191406</v>
       </c>
       <c r="C177" t="n">
         <v>107.4700012207031</v>
@@ -5126,7 +5126,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>86.81465911865234</v>
+        <v>86.81465148925781</v>
       </c>
       <c r="C178" t="n">
         <v>103.9199981689453</v>
@@ -5155,7 +5155,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>84.01607513427734</v>
+        <v>84.01606750488281</v>
       </c>
       <c r="C179" t="n">
         <v>100.5699996948242</v>
@@ -5184,7 +5184,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>94.98486328125</v>
+        <v>94.98487854003906</v>
       </c>
       <c r="C180" t="n">
         <v>113.6999969482422</v>
@@ -5242,7 +5242,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>93.46949005126953</v>
+        <v>93.46947479248047</v>
       </c>
       <c r="C182" t="n">
         <v>111.3300018310547</v>
@@ -5271,7 +5271,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>98.20465850830078</v>
+        <v>98.20467376708984</v>
       </c>
       <c r="C183" t="n">
         <v>116.9700012207031</v>
@@ -5300,7 +5300,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>99.67710113525391</v>
+        <v>99.67710876464844</v>
       </c>
       <c r="C184" t="n">
         <v>118.129997253418</v>
@@ -5329,7 +5329,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>110.4692230224609</v>
+        <v>110.46923828125</v>
       </c>
       <c r="C185" t="n">
         <v>130.9199981689453</v>
@@ -5416,7 +5416,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>111.3573608398438</v>
+        <v>111.3573455810547</v>
       </c>
       <c r="C188" t="n">
         <v>131.3099975585938</v>
@@ -5445,7 +5445,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>113.1976089477539</v>
+        <v>113.197624206543</v>
       </c>
       <c r="C189" t="n">
         <v>133.4799957275391</v>
@@ -5474,7 +5474,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>106.8250579833984</v>
+        <v>106.8250198364258</v>
       </c>
       <c r="C190" t="n">
         <v>125.3499984741211</v>
@@ -5503,7 +5503,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>102.1463851928711</v>
+        <v>102.1463775634766</v>
       </c>
       <c r="C191" t="n">
         <v>119.8600006103516</v>
@@ -5532,7 +5532,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>90.93124389648438</v>
+        <v>90.93125152587891</v>
       </c>
       <c r="C192" t="n">
         <v>106.6999969482422</v>
@@ -5561,7 +5561,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>88.72312927246094</v>
+        <v>88.72313690185547</v>
       </c>
       <c r="C193" t="n">
         <v>103.4499969482422</v>
@@ -5590,7 +5590,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>88.75745391845703</v>
+        <v>88.7574462890625</v>
       </c>
       <c r="C194" t="n">
         <v>103.4899978637695</v>
@@ -5706,7 +5706,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>86.40568542480469</v>
+        <v>86.40569305419922</v>
       </c>
       <c r="C198" t="n">
         <v>100.1500015258789</v>
@@ -5735,7 +5735,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>78.02744293212891</v>
+        <v>78.02745819091797</v>
       </c>
       <c r="C199" t="n">
         <v>89.75</v>
@@ -5764,7 +5764,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>80.43565368652344</v>
+        <v>80.43566131591797</v>
       </c>
       <c r="C200" t="n">
         <v>92.51999664306641</v>
@@ -5793,7 +5793,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>76.43647766113281</v>
+        <v>76.43647003173828</v>
       </c>
       <c r="C201" t="n">
         <v>87.91999816894531</v>
@@ -5822,7 +5822,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>70.76426696777344</v>
+        <v>70.7642822265625</v>
       </c>
       <c r="C202" t="n">
         <v>80.75</v>
@@ -5880,7 +5880,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>69.2657470703125</v>
+        <v>69.26573181152344</v>
       </c>
       <c r="C204" t="n">
         <v>79.04000091552734</v>
@@ -5909,7 +5909,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>68.71485900878906</v>
+        <v>68.71483612060547</v>
       </c>
       <c r="C205" t="n">
         <v>77.72000122070312</v>
@@ -5967,7 +5967,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>73.20624542236328</v>
+        <v>73.20625305175781</v>
       </c>
       <c r="C207" t="n">
         <v>82.80000305175781</v>
@@ -5996,7 +5996,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>71.89037322998047</v>
+        <v>71.890380859375</v>
       </c>
       <c r="C208" t="n">
         <v>80.62000274658203</v>
@@ -6025,7 +6025,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>81.10182189941406</v>
+        <v>81.10181427001953</v>
       </c>
       <c r="C209" t="n">
         <v>90.94999694824219</v>
@@ -6083,7 +6083,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>79.17900848388672</v>
+        <v>79.17900085449219</v>
       </c>
       <c r="C211" t="n">
         <v>88.09999847412109</v>
@@ -6141,7 +6141,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>73.24732971191406</v>
+        <v>73.247314453125</v>
       </c>
       <c r="C213" t="n">
         <v>81.5</v>
@@ -6170,7 +6170,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>71.02677154541016</v>
+        <v>71.02674865722656</v>
       </c>
       <c r="C214" t="n">
         <v>78.36000061035156</v>
@@ -6199,7 +6199,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>63.95671081542969</v>
+        <v>63.95670700073242</v>
       </c>
       <c r="C215" t="n">
         <v>70.55999755859375</v>
@@ -6228,7 +6228,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>71.85158538818359</v>
+        <v>71.85157775878906</v>
       </c>
       <c r="C216" t="n">
         <v>79.26999664306641</v>
@@ -6257,7 +6257,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>75.29605102539062</v>
+        <v>75.29604339599609</v>
       </c>
       <c r="C217" t="n">
         <v>82.37999725341797</v>
@@ -6286,7 +6286,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>80.01233673095703</v>
+        <v>80.0123291015625</v>
       </c>
       <c r="C218" t="n">
         <v>87.54000091552734</v>
@@ -6344,7 +6344,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>80.31528472900391</v>
+        <v>80.31529998779297</v>
       </c>
       <c r="C220" t="n">
         <v>87.15000152587891</v>
@@ -6373,7 +6373,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>73.94720458984375</v>
+        <v>73.94719696044922</v>
       </c>
       <c r="C221" t="n">
         <v>80.23999786376953</v>
@@ -6402,7 +6402,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>74.98858642578125</v>
+        <v>74.98857879638672</v>
       </c>
       <c r="C222" t="n">
         <v>81.37000274658203</v>
@@ -6431,7 +6431,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>73.18295288085938</v>
+        <v>73.18294525146484</v>
       </c>
       <c r="C223" t="n">
         <v>78.70999908447266</v>
@@ -6460,7 +6460,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>74.67990112304688</v>
+        <v>74.67988586425781</v>
       </c>
       <c r="C224" t="n">
         <v>80.31999969482422</v>
@@ -6489,7 +6489,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>82.35988616943359</v>
+        <v>82.35987854003906</v>
       </c>
       <c r="C225" t="n">
         <v>88.58000183105469</v>
@@ -6518,7 +6518,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>84.36829376220703</v>
+        <v>84.36830139160156</v>
       </c>
       <c r="C226" t="n">
         <v>90.02999877929688</v>
@@ -6547,7 +6547,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>83.63733673095703</v>
+        <v>83.63734436035156</v>
       </c>
       <c r="C227" t="n">
         <v>89.25</v>
@@ -6605,7 +6605,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>75.50430297851562</v>
+        <v>75.50428771972656</v>
       </c>
       <c r="C229" t="n">
         <v>79.87999725341797</v>
@@ -6634,7 +6634,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>85.84503173828125</v>
+        <v>85.84501647949219</v>
       </c>
       <c r="C230" t="n">
         <v>90.81999969482422</v>
@@ -6663,7 +6663,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>86.97929382324219</v>
+        <v>86.97928619384766</v>
       </c>
       <c r="C231" t="n">
         <v>92.01999664306641</v>
@@ -6721,7 +6721,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>80.75225830078125</v>
+        <v>80.75226593017578</v>
       </c>
       <c r="C233" t="n">
         <v>84.76000213623047</v>
@@ -6750,7 +6750,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>79.05642700195312</v>
+        <v>79.05641937255859</v>
       </c>
       <c r="C234" t="n">
         <v>82.98000335693359</v>
@@ -6779,7 +6779,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>83.73818206787109</v>
+        <v>83.73818969726562</v>
       </c>
       <c r="C235" t="n">
         <v>87.16999816894531</v>
@@ -6837,7 +6837,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>89.15614318847656</v>
+        <v>89.1561279296875</v>
       </c>
       <c r="C237" t="n">
         <v>92.80999755859375</v>
@@ -6895,7 +6895,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>87.79019165039062</v>
+        <v>87.79019927978516</v>
       </c>
       <c r="C239" t="n">
         <v>90.69999694824219</v>
@@ -6924,7 +6924,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>101.9508438110352</v>
+        <v>101.9508361816406</v>
       </c>
       <c r="C240" t="n">
         <v>105.3300018310547</v>
@@ -7011,7 +7011,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>95.22195434570312</v>
+        <v>95.22196197509766</v>
       </c>
       <c r="C243" t="n">
         <v>97.66000366210938</v>
